--- a/artfynd/A 48562-2024 artfynd.xlsx
+++ b/artfynd/A 48562-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111726529</v>
+        <v>111726522</v>
       </c>
       <c r="B2" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565481</v>
+        <v>565482</v>
       </c>
       <c r="R2" t="n">
-        <v>7032669</v>
+        <v>7032674</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,12 +779,7 @@
         <v>111726527</v>
       </c>
       <c r="B3" t="n">
-        <v>81248</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111726522</v>
+        <v>111726524</v>
       </c>
       <c r="B4" t="n">
-        <v>81248</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565483</v>
+        <v>565535</v>
       </c>
       <c r="R4" t="n">
-        <v>7032674</v>
+        <v>7032545</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111726524</v>
+        <v>111726529</v>
       </c>
       <c r="B5" t="n">
-        <v>98508</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565535</v>
+        <v>565481</v>
       </c>
       <c r="R5" t="n">
-        <v>7032545</v>
+        <v>7032669</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111726530</v>
+        <v>111726539</v>
       </c>
       <c r="B6" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565450</v>
+        <v>565357</v>
       </c>
       <c r="R6" t="n">
-        <v>7032630</v>
+        <v>7032721</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,12 +1183,7 @@
         <v>111726528</v>
       </c>
       <c r="B7" t="n">
-        <v>73696</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,6 +1274,213 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>111726530</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Storflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>565450</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7032630</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>111726525</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Storflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>565661</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7032489</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>på rönn</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 48562-2024 artfynd.xlsx
+++ b/artfynd/A 48562-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111726522</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111726527</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111726524</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111726529</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111726539</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111726528</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111726525</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,8 +1525,23 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111726530</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>